--- a/data/reading_lessons.xlsx
+++ b/data/reading_lessons.xlsx
@@ -60397,12 +60397,12 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>КОН</t>
+          <t>КАН</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>[kɔn]</t>
+          <t>[kan]</t>
         </is>
       </c>
     </row>
@@ -61819,7 +61819,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>ЗIMA</t>
+          <t>ЗИМА</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -68836,6 +68836,11 @@
       <c r="B56" t="n">
         <v>55</v>
       </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="D56" t="inlineStr">
         <is>
           <t>[na]</t>
@@ -70903,12 +70908,12 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>CON</t>
+          <t>CAN</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>[kon]</t>
+          <t>[kan]</t>
         </is>
       </c>
     </row>
@@ -80931,7 +80936,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t xml:space="preserve">치마 </t>
+          <t>치마</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -90946,7 +90951,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arzt </t>
+          <t>Arzt</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -90964,12 +90969,12 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Park</t>
+          <t>Park</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [paʁk]</t>
+          <t>[paʁk]</t>
         </is>
       </c>
     </row>
@@ -91221,7 +91226,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [uːʁ]</t>
+          <t>[uːʁ]</t>
         </is>
       </c>
     </row>

--- a/data/reading_lessons.xlsx
+++ b/data/reading_lessons.xlsx
@@ -81827,22 +81827,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Ii, Yy в бу [ı]: 'funny ['fʌnı]; mini ['mını].</t>
+          <t>Ii, Yy в безударном слоге читаются как [ı]: 'funny ['fʌnı]; mini ['mını].</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ii, Yy in bu [ı]: 'funny ['fʌnı]; mini ['mını].</t>
+          <t>Ii, Yy in an unstressed syllable are pronounced as [ı]: 'funny ['fʌnı]; mini ['mını].</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Ii, Yy en bu [ı]: 'funny ['fʌnı]; mini ['mını].</t>
+          <t>Ii, Yy en sílaba átona se pronuncian como [ı]: 'funny ['fʌnı]; mini ['mını].</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ii, Yy у bu [ı]: 'funny ['fʌnı]; mini ['mını].</t>
+          <t>Ii, Yy у ненаголошеному складі читаються як [ı]: 'funny ['fʌnı]; mini ['mını].</t>
         </is>
       </c>
     </row>
@@ -82877,12 +82877,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Буква о в буквосочетаниях old ost olt читается как [əʊ]: old [əʊld ]; most [məʊst]; bolt [bəʊlt].</t>
+          <t>Буква о в буквосочетаниях old ost olt читается как [əʊ]: old [əʊld]; most [məʊst]; bolt [bəʊlt].</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>The letter o in the letter combinations old ost olt is pronounced [əʊ]: old [əʊld ]; most [məʊst]; bolt [bəʊlt].</t>
+          <t>The letter o in the letter combinations old ost olt is pronounced [əʊ]: old [əʊld]; most [məʊst]; bolt [bəʊlt].</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -82892,7 +82892,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Літера o у буквосполученнях old ost olt вимовляється як [əʊ]: old [əʊld ]; most [məʊst]; bolt [bəʊlt].</t>
+          <t>Літера o у буквосполученнях old ost olt вимовляється як [əʊ]: old [əʊld]; most [məʊst]; bolt [bəʊlt].</t>
         </is>
       </c>
     </row>
@@ -83052,12 +83052,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Буквосочетание tion  читается как [ʃ(ə)n]: 'action ]'ækʃ(ə)n]. Буквосочетание ture читается как [tʃə]: 'nature ['neıtʃə].</t>
+          <t>Буквосочетание tion  читается как [ʃ(ə)n]: 'action ['ækʃ(ə)n]. Буквосочетание ture читается как [tʃə]: 'nature ['neıtʃə].</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>The letter combination tion is read as [ʃ(ə)n]: 'action ]'ækʃ(ə)n]. The letter combination ture is read as [tʃə]: 'nature ['neıtʃə].</t>
+          <t>The letter combination tion is read as [ʃ(ə)n]: 'action ['ækʃ(ə)n]. The letter combination ture is read as [tʃə]: 'nature ['neıtʃə].</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -83067,7 +83067,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Буквосполучення tion читається як [ʃ(ə)n]: 'action ]'ækʃ(ə)n]. Буквосполучення ture читається як [tʃə]: 'nature ['neıtʃə].</t>
+          <t>Буквосполучення tion читається як [ʃ(ə)n]: 'action ['ækʃ(ə)n]. Буквосполучення ture читається як [tʃə]: 'nature ['neıtʃə].</t>
         </is>
       </c>
     </row>
